--- a/www/terminologies/ValueSet-jdv-rcp-organe-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-rcp-organe-cisis.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141840</t>
+    <t>20260220142105</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:40+01:00</t>
+    <t>2026-02-20T14:21:05+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -102,12 +102,84 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>C85</t>
+  </si>
+  <si>
+    <t>Lymphome non hodgkinien, de types autres et non précisés</t>
+  </si>
+  <si>
     <t>C88</t>
   </si>
   <si>
     <t>Maladies immunoprolifératives malignes</t>
   </si>
   <si>
+    <t>C81</t>
+  </si>
+  <si>
+    <t>Lymphome de Hodgkin</t>
+  </si>
+  <si>
+    <t>C95.1</t>
+  </si>
+  <si>
+    <t>Leucémie chronique à cellules non précisées</t>
+  </si>
+  <si>
+    <t>C91.1</t>
+  </si>
+  <si>
+    <t>Leucémie lymphoïde chronique à cellules B</t>
+  </si>
+  <si>
+    <t>C91.0</t>
+  </si>
+  <si>
+    <t>Leucémie lymphoblastique aigüe [LLA]</t>
+  </si>
+  <si>
+    <t>C92</t>
+  </si>
+  <si>
+    <t>Leucémie myéloïde</t>
+  </si>
+  <si>
+    <t>C92.0</t>
+  </si>
+  <si>
+    <t>Leucémie myéloblastique aigüe [LAM]</t>
+  </si>
+  <si>
+    <t>C92.1</t>
+  </si>
+  <si>
+    <t>Leucémie myéloïde chronique [LMC] ABL-BCR positif</t>
+  </si>
+  <si>
+    <t>C93.0</t>
+  </si>
+  <si>
+    <t>Leucémie monoblastique/monocytaire aigüe</t>
+  </si>
+  <si>
+    <t>C95.0</t>
+  </si>
+  <si>
+    <t>Leucémie aiguë à cellules non précisées</t>
+  </si>
+  <si>
+    <t>C94.6</t>
+  </si>
+  <si>
+    <t>Maladie myélodysplasique et myéloproliférative, non classée ailleurs</t>
+  </si>
+  <si>
+    <t>C90.0</t>
+  </si>
+  <si>
+    <t>Myélome multiple</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -115,78 +187,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/sid/icd-10</t>
-  </si>
-  <si>
-    <t>C3211</t>
-  </si>
-  <si>
-    <t>lymphome non hodgkinien</t>
-  </si>
-  <si>
-    <t>C9357</t>
-  </si>
-  <si>
-    <t>Lymphome de Hodgkin</t>
-  </si>
-  <si>
-    <t>C3483</t>
-  </si>
-  <si>
-    <t>leucémie chronique</t>
-  </si>
-  <si>
-    <t>C3163</t>
-  </si>
-  <si>
-    <t>Leucémie lymphocytique chronique</t>
-  </si>
-  <si>
-    <t>C3167</t>
-  </si>
-  <si>
-    <t>Leucémie lymphoblastique aiguë</t>
-  </si>
-  <si>
-    <t>C3172</t>
-  </si>
-  <si>
-    <t>Leucémie myéloïde</t>
-  </si>
-  <si>
-    <t>C3171</t>
-  </si>
-  <si>
-    <t>leucémie myéloïde aiguë</t>
-  </si>
-  <si>
-    <t>C3174</t>
-  </si>
-  <si>
-    <t>leucémie myéloïde chronique BCR-ABL positive</t>
-  </si>
-  <si>
-    <t>C4861</t>
-  </si>
-  <si>
-    <t>leucémie monocytaire aiguë</t>
-  </si>
-  <si>
-    <t>C9300</t>
-  </si>
-  <si>
-    <t>leucémie aiguë</t>
-  </si>
-  <si>
-    <t>C27262</t>
-  </si>
-  <si>
-    <t>maladies myélodysplasiques-myéloprolifératives</t>
-  </si>
-  <si>
-    <t>C3242</t>
-  </si>
-  <si>
-    <t>myélome à cellules plasmatiques</t>
   </si>
   <si>
     <t>C94529</t>
@@ -723,7 +723,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -751,15 +751,111 @@
         <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -769,7 +865,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -786,129 +882,33 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>34</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B17" t="s" s="2">
         <v>61</v>
       </c>
     </row>
@@ -960,15 +960,15 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>30</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s" s="2">
         <v>68</v>
@@ -1310,15 +1310,15 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>30</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>147</v>

--- a/www/terminologies/ValueSet-jdv-rcp-organe-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-rcp-organe-cisis.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142105</t>
+    <t>20260311144904</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:05+01:00</t>
+    <t>2026-03-11T14:49:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-rcp-organe-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-rcp-organe-cisis.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144904</t>
+    <t>20260420150251</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:04+01:00</t>
+    <t>2026-04-20T15:02:51+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-rcp-organe-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-rcp-organe-cisis.xlsx
@@ -8,12 +8,15 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
+    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="148">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260619134043</t>
+    <t>20260420150251</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:40:43+01:00</t>
+    <t>2026-04-20T15:02:51+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -99,136 +102,349 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>118599009</t>
-  </si>
-  <si>
-    <t>lymphome hodgkinien</t>
-  </si>
-  <si>
-    <t>118601006</t>
-  </si>
-  <si>
-    <t>lymphome non hodgkinien</t>
-  </si>
-  <si>
-    <t>93143009</t>
-  </si>
-  <si>
-    <t>leucémie</t>
-  </si>
-  <si>
-    <t>445738007</t>
-  </si>
-  <si>
-    <t>maladie myéloproliférative et syndrome myélodysplasique</t>
-  </si>
-  <si>
-    <t>109989006</t>
-  </si>
-  <si>
-    <t>myélome multiple</t>
-  </si>
-  <si>
-    <t>297260006</t>
-  </si>
-  <si>
-    <t>hypophyse et/ou épiphyse</t>
-  </si>
-  <si>
-    <t>86394004</t>
-  </si>
-  <si>
-    <t>canal crâniopharyngien</t>
+    <t>C85</t>
+  </si>
+  <si>
+    <t>Lymphome non hodgkinien, de types autres et non précisés</t>
+  </si>
+  <si>
+    <t>C88</t>
+  </si>
+  <si>
+    <t>Maladies immunoprolifératives malignes</t>
+  </si>
+  <si>
+    <t>C81</t>
+  </si>
+  <si>
+    <t>Lymphome de Hodgkin</t>
+  </si>
+  <si>
+    <t>C95.1</t>
+  </si>
+  <si>
+    <t>Leucémie chronique à cellules non précisées</t>
+  </si>
+  <si>
+    <t>C91.1</t>
+  </si>
+  <si>
+    <t>Leucémie lymphoïde chronique à cellules B</t>
+  </si>
+  <si>
+    <t>C91.0</t>
+  </si>
+  <si>
+    <t>Leucémie lymphoblastique aigüe [LLA]</t>
+  </si>
+  <si>
+    <t>C92</t>
+  </si>
+  <si>
+    <t>Leucémie myéloïde</t>
+  </si>
+  <si>
+    <t>C92.0</t>
+  </si>
+  <si>
+    <t>Leucémie myéloblastique aigüe [LAM]</t>
+  </si>
+  <si>
+    <t>C92.1</t>
+  </si>
+  <si>
+    <t>Leucémie myéloïde chronique [LMC] ABL-BCR positif</t>
+  </si>
+  <si>
+    <t>C93.0</t>
+  </si>
+  <si>
+    <t>Leucémie monoblastique/monocytaire aigüe</t>
+  </si>
+  <si>
+    <t>C95.0</t>
+  </si>
+  <si>
+    <t>Leucémie aiguë à cellules non précisées</t>
+  </si>
+  <si>
+    <t>C94.6</t>
+  </si>
+  <si>
+    <t>Maladie myélodysplasique et myéloproliférative, non classée ailleurs</t>
+  </si>
+  <si>
+    <t>C90.0</t>
+  </si>
+  <si>
+    <t>Myélome multiple</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/sid/icd-10</t>
+  </si>
+  <si>
+    <t>C94529</t>
+  </si>
+  <si>
+    <t>région vulvo-vaginale</t>
+  </si>
+  <si>
+    <t>C12664</t>
+  </si>
+  <si>
+    <t>Péritoine-rétropéritoine</t>
+  </si>
+  <si>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl</t>
+  </si>
+  <si>
+    <t>MED-237</t>
+  </si>
+  <si>
+    <t>Fosses nasales, sinus, oreille moy/int</t>
+  </si>
+  <si>
+    <t>MED-251</t>
+  </si>
+  <si>
+    <t>Colon-Rectum-Anus</t>
+  </si>
+  <si>
+    <t>MED-255</t>
+  </si>
+  <si>
+    <t>Trachée, Bronches, Poumon</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
+  </si>
+  <si>
+    <t>57171008</t>
+  </si>
+  <si>
+    <t>système hématopoïétique</t>
+  </si>
+  <si>
+    <t>119253004</t>
+  </si>
+  <si>
+    <t>voies aérodigestives supérieures</t>
+  </si>
+  <si>
+    <t>303270005</t>
+  </si>
+  <si>
+    <t>foie et/ou voies biliaires</t>
+  </si>
+  <si>
+    <t>39937001</t>
+  </si>
+  <si>
+    <t>peau</t>
+  </si>
+  <si>
+    <t>76752008</t>
+  </si>
+  <si>
+    <t>sein</t>
+  </si>
+  <si>
+    <t>306721000</t>
+  </si>
+  <si>
+    <t>os et/ou articulation</t>
+  </si>
+  <si>
+    <t>87784001</t>
+  </si>
+  <si>
+    <t>tissus mous</t>
+  </si>
+  <si>
+    <t>312419003</t>
+  </si>
+  <si>
+    <t>appareil respiratoire et/ou cavité thoracique</t>
+  </si>
+  <si>
+    <t>4596009</t>
+  </si>
+  <si>
+    <t>larynx</t>
+  </si>
+  <si>
+    <t>3120008</t>
+  </si>
+  <si>
+    <t>plèvre</t>
+  </si>
+  <si>
+    <t>86762007</t>
+  </si>
+  <si>
+    <t>système digestif</t>
+  </si>
+  <si>
+    <t>74262004</t>
+  </si>
+  <si>
+    <t>cavité orale</t>
+  </si>
+  <si>
+    <t>48477009</t>
+  </si>
+  <si>
+    <t>lèvre</t>
+  </si>
+  <si>
+    <t>21974007</t>
+  </si>
+  <si>
+    <t>langue</t>
+  </si>
+  <si>
+    <t>54066008</t>
+  </si>
+  <si>
+    <t>pharynx</t>
+  </si>
+  <si>
+    <t>32849002</t>
+  </si>
+  <si>
+    <t>œsophage</t>
+  </si>
+  <si>
+    <t>69695003</t>
+  </si>
+  <si>
+    <t>estomac</t>
+  </si>
+  <si>
+    <t>30315005</t>
+  </si>
+  <si>
+    <t>intestin grêle</t>
+  </si>
+  <si>
+    <t>385294005</t>
+  </si>
+  <si>
+    <t>glande salivaire</t>
+  </si>
+  <si>
+    <t>15776009</t>
+  </si>
+  <si>
+    <t>pancréas</t>
+  </si>
+  <si>
+    <t>122489005</t>
+  </si>
+  <si>
+    <t>système urinaire</t>
+  </si>
+  <si>
+    <t>431491007</t>
+  </si>
+  <si>
+    <t>voies urinaires supérieures proprement dites</t>
+  </si>
+  <si>
+    <t>64033007</t>
+  </si>
+  <si>
+    <t>rein</t>
+  </si>
+  <si>
+    <t>89837001</t>
+  </si>
+  <si>
+    <t>vessie</t>
+  </si>
+  <si>
+    <t>53065001</t>
+  </si>
+  <si>
+    <t>appareil génital féminin</t>
+  </si>
+  <si>
+    <t>23952005</t>
+  </si>
+  <si>
+    <t>corps de l'utérus</t>
+  </si>
+  <si>
+    <t>71252005</t>
+  </si>
+  <si>
+    <t>col utérin</t>
+  </si>
+  <si>
+    <t>15497006</t>
+  </si>
+  <si>
+    <t>ovaire</t>
+  </si>
+  <si>
+    <t>90264002</t>
+  </si>
+  <si>
+    <t>appareil génital masculin</t>
+  </si>
+  <si>
+    <t>18911002</t>
+  </si>
+  <si>
+    <t>pénis</t>
+  </si>
+  <si>
+    <t>41216001</t>
+  </si>
+  <si>
+    <t>prostate</t>
+  </si>
+  <si>
+    <t>40689003</t>
+  </si>
+  <si>
+    <t>testicule</t>
+  </si>
+  <si>
+    <t>21483005</t>
+  </si>
+  <si>
+    <t>système nerveux central</t>
+  </si>
+  <si>
+    <t>84782009</t>
+  </si>
+  <si>
+    <t>nerf périphérique</t>
   </si>
   <si>
     <t>81745001</t>
   </si>
   <si>
-    <t>œil proprement dit</t>
-  </si>
-  <si>
-    <t>39937001</t>
-  </si>
-  <si>
-    <t>peau</t>
-  </si>
-  <si>
-    <t>76752008</t>
-  </si>
-  <si>
-    <t>sein</t>
-  </si>
-  <si>
-    <t>306721000</t>
-  </si>
-  <si>
-    <t>os et/ou articulation</t>
-  </si>
-  <si>
-    <t>87784001</t>
-  </si>
-  <si>
-    <t>tissus mous</t>
-  </si>
-  <si>
-    <t>53912006</t>
-  </si>
-  <si>
-    <t>fosse nasale</t>
-  </si>
-  <si>
-    <t>25342003</t>
-  </si>
-  <si>
-    <t>oreille moyenne</t>
-  </si>
-  <si>
-    <t>2095001</t>
-  </si>
-  <si>
-    <t>sinus paranasaux</t>
-  </si>
-  <si>
-    <t>74262004</t>
-  </si>
-  <si>
-    <t>cavité orale</t>
-  </si>
-  <si>
-    <t>48477009</t>
-  </si>
-  <si>
-    <t>lèvre</t>
-  </si>
-  <si>
-    <t>21974007</t>
-  </si>
-  <si>
-    <t>langue</t>
-  </si>
-  <si>
-    <t>312535008</t>
-  </si>
-  <si>
-    <t>pharynx et/ou larynx</t>
-  </si>
-  <si>
-    <t>9875009</t>
-  </si>
-  <si>
-    <t>thymus</t>
-  </si>
-  <si>
-    <t>385294005</t>
-  </si>
-  <si>
-    <t>glande salivaire</t>
-  </si>
-  <si>
-    <t>111002</t>
-  </si>
-  <si>
-    <t>glande parathyroïde</t>
+    <t>œil</t>
+  </si>
+  <si>
+    <t>387910009</t>
+  </si>
+  <si>
+    <t>glande endocrine</t>
+  </si>
+  <si>
+    <t>23451007</t>
+  </si>
+  <si>
+    <t>glande suprarénale</t>
   </si>
   <si>
     <t>69748006</t>
@@ -241,180 +457,6 @@
   </si>
   <si>
     <t>médiastin</t>
-  </si>
-  <si>
-    <t>80891009</t>
-  </si>
-  <si>
-    <t>cœur</t>
-  </si>
-  <si>
-    <t>76848001</t>
-  </si>
-  <si>
-    <t>péricarde</t>
-  </si>
-  <si>
-    <t>91724006</t>
-  </si>
-  <si>
-    <t>arbre trachéobronchique</t>
-  </si>
-  <si>
-    <t>39607008</t>
-  </si>
-  <si>
-    <t>poumon</t>
-  </si>
-  <si>
-    <t>3120008</t>
-  </si>
-  <si>
-    <t>plèvre</t>
-  </si>
-  <si>
-    <t>32849002</t>
-  </si>
-  <si>
-    <t>œsophage</t>
-  </si>
-  <si>
-    <t>15425007</t>
-  </si>
-  <si>
-    <t>péritoine</t>
-  </si>
-  <si>
-    <t>303270005</t>
-  </si>
-  <si>
-    <t>foie et/ou voies biliaires</t>
-  </si>
-  <si>
-    <t>15776009</t>
-  </si>
-  <si>
-    <t>pancréas</t>
-  </si>
-  <si>
-    <t>69695003</t>
-  </si>
-  <si>
-    <t>estomac</t>
-  </si>
-  <si>
-    <t>30315005</t>
-  </si>
-  <si>
-    <t>intestin grêle</t>
-  </si>
-  <si>
-    <t>14742008</t>
-  </si>
-  <si>
-    <t>gros intestin</t>
-  </si>
-  <si>
-    <t>53505006</t>
-  </si>
-  <si>
-    <t>anus</t>
-  </si>
-  <si>
-    <t>431491007</t>
-  </si>
-  <si>
-    <t>voies urinaires hautes proprement dites</t>
-  </si>
-  <si>
-    <t>64033007</t>
-  </si>
-  <si>
-    <t>rein</t>
-  </si>
-  <si>
-    <t>23451007</t>
-  </si>
-  <si>
-    <t>glande surrénale</t>
-  </si>
-  <si>
-    <t>89837001</t>
-  </si>
-  <si>
-    <t>vessie</t>
-  </si>
-  <si>
-    <t>45292006</t>
-  </si>
-  <si>
-    <t>vulve</t>
-  </si>
-  <si>
-    <t>76784001</t>
-  </si>
-  <si>
-    <t>vagin</t>
-  </si>
-  <si>
-    <t>78067005</t>
-  </si>
-  <si>
-    <t>placenta</t>
-  </si>
-  <si>
-    <t>23952005</t>
-  </si>
-  <si>
-    <t>corps de l'utérus</t>
-  </si>
-  <si>
-    <t>71252005</t>
-  </si>
-  <si>
-    <t>col de l'utérus</t>
-  </si>
-  <si>
-    <t>15497006</t>
-  </si>
-  <si>
-    <t>ovaire</t>
-  </si>
-  <si>
-    <t>18911002</t>
-  </si>
-  <si>
-    <t>pénis</t>
-  </si>
-  <si>
-    <t>41216001</t>
-  </si>
-  <si>
-    <t>prostate</t>
-  </si>
-  <si>
-    <t>40689003</t>
-  </si>
-  <si>
-    <t>testicule</t>
-  </si>
-  <si>
-    <t>21483005</t>
-  </si>
-  <si>
-    <t>système nerveux central</t>
-  </si>
-  <si>
-    <t>84782009</t>
-  </si>
-  <si>
-    <t>nerf périphérique</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
   </si>
   <si>
     <t>http://snomed.info/sct</t>
@@ -681,7 +723,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -805,327 +847,481 @@
         <v>54</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>56</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B42"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>97</v>
+      </c>
       <c r="B16" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>59</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>61</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>63</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>65</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>67</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>69</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>71</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>73</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>77</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>79</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>81</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>83</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>85</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>87</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>89</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>91</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>93</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>95</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>97</v>
+        <v>138</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>103</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>105</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>107</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>134</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-jdv-rcp-organe-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-rcp-organe-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260619134043</t>
+    <t>20260716085853</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:40:43+01:00</t>
+    <t>2026-07-16T08:58:53+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
